--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241025120000</t>
+    <t>20241209120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T12:00:00+01:00</t>
+    <t>2024-12-09T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1869,24 +1869,6 @@
     <t>Bypass gastrique</t>
   </si>
   <si>
-    <t>0535</t>
-  </si>
-  <si>
-    <t>Prise en charge de l'obésité modérée</t>
-  </si>
-  <si>
-    <t>0536</t>
-  </si>
-  <si>
-    <t>Prise en charge de l'obésité sévère</t>
-  </si>
-  <si>
-    <t>0537</t>
-  </si>
-  <si>
-    <t>Prise en charge de l'obésité morbide</t>
-  </si>
-  <si>
     <t>0538</t>
   </si>
   <si>
@@ -2859,12 +2841,6 @@
     <t>Actions de prévention tertiaire (pour éviter l'aggravation ou la chronicisation d'un problème de santé)</t>
   </si>
   <si>
-    <t>0745</t>
-  </si>
-  <si>
-    <t>Réadaptation des séquelles de brûlures</t>
-  </si>
-  <si>
     <t>0746</t>
   </si>
   <si>
@@ -4743,12 +4719,6 @@
     <t>Réadaptation des affections malformatives du système musculo-squelettique</t>
   </si>
   <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>Réadaptation des affections médullaires</t>
-  </si>
-  <si>
     <t>1107</t>
   </si>
   <si>
@@ -6726,7 +6696,7 @@
     <t>1454</t>
   </si>
   <si>
-    <t>Evaluation et suivi standardisé clinique et paraclinique des commotions cérébrales</t>
+    <t>Evaluation et suivi standardisé clinique et paraclinique des commotions cérébrales (Traumatisme Crânien Léger - TCL)</t>
   </si>
   <si>
     <t>1455</t>
@@ -6738,7 +6708,7 @@
     <t>1456</t>
   </si>
   <si>
-    <t>Soins et surveillance de remplissage de pompe à morphine</t>
+    <t>Soins et surveillance de remplissage de pompe à antalgique (dont morphine)</t>
   </si>
   <si>
     <t>1457</t>
@@ -6925,6 +6895,36 @@
   </si>
   <si>
     <t>Télésurveillance médicale en oncologie</t>
+  </si>
+  <si>
+    <t>1488</t>
+  </si>
+  <si>
+    <t>Electrostimulation fonctionnelle urologique</t>
+  </si>
+  <si>
+    <t>1489</t>
+  </si>
+  <si>
+    <t>Filière Obésité – Niveau 1 (Conventionné CSO)</t>
+  </si>
+  <si>
+    <t>1490</t>
+  </si>
+  <si>
+    <t>Filière Obésité – Niveau 2 (Conventionné CSO)</t>
+  </si>
+  <si>
+    <t>1491</t>
+  </si>
+  <si>
+    <t>Filière Obésité – Niveau 3 (Conventionné CSO)</t>
+  </si>
+  <si>
+    <t>1492</t>
+  </si>
+  <si>
+    <t>Filière Obésité – Niveau 3 (Centre Spécialisé Obésité)</t>
   </si>
   <si>
     <t/>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="2307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="2311">
   <si>
     <t>Property</t>
   </si>
@@ -1867,6 +1867,18 @@
   </si>
   <si>
     <t>Bypass gastrique</t>
+  </si>
+  <si>
+    <t>0536</t>
+  </si>
+  <si>
+    <t>Prise en charge de l'obésité sévère</t>
+  </si>
+  <si>
+    <t>0537</t>
+  </si>
+  <si>
+    <t>Prise en charge de l'obésité morbide</t>
   </si>
   <si>
     <t>0538</t>
@@ -7203,7 +7215,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1140"/>
+  <dimension ref="A1:B1142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -16319,15 +16331,31 @@
         <v>2304</v>
       </c>
       <c r="B1139" t="s" s="2">
-        <v>2304</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="s" s="2">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="B1140" t="s" s="2">
-        <v>2306</v>
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="s" s="2">
+        <v>2308</v>
+      </c>
+      <c r="B1141" t="s" s="2">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="s" s="2">
+        <v>2309</v>
+      </c>
+      <c r="B1142" t="s" s="2">
+        <v>2310</v>
       </c>
     </row>
   </sheetData>
